--- a/data_extactor/batch_10_fa/batch_0034_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0034_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Philosophy and Religion Teachers, Postsecondary (اساتید فلسفه و دین، پس از متوسطه)</t>
+          <t>اساتید فلسفه و دین، پس از متوسطه (Philosophy and Religion Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Assistant Professor | Associate Professor | Humanities Professor | Instructor | Philosophy Instructor | Philosophy Professor | Professor | Religion Professor | Religious Studies Professor | Theology Professor</t>
+          <t>استادیار | دانشیار | استاد علوم انسانی | مدرس | مدرس فلسفه | استاد فلسفه | استاد | استاد دین‌شناسی | استاد مطالعات دینی | استاد الهیات</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Blackboard Learn | Collaborative editing software | Course management system software | DOC Cop | Desire2Learn LMS software | Email software | Gateway to Logic | Google Docs | Image scanning software | InteLext Past Masters | Learning management system LMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Philosopher's Information Center The Philosopher's Index | Sakai CLE | University of California Thesaurus Linguae Graecae TLG | Web browser software | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Gateway to Logic | Google Docs | نرم‌افزار اسکن تصویر | InteLext Past Masters | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Philosopher's Information Center The Philosopher's Index | Sakai CLE | University of California Thesaurus Linguae Graecae TLG | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Active Listening | Speaking | Writing | Critical Thinking | Learning Strategies | Active Learning | Monitoring</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Philosophy and Theology | English Language | Education and Training | History and Archeology | Sociology and Anthropology | Law and Government</t>
+          <t>فلسفه و الهیات | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Written Comprehension | Oral Expression | Speech Clarity | Oral Comprehension | Written Expression | Inductive Reasoning | Deductive Reasoning | Near Vision | Problem Sensitivity | Speech Recognition | Category Flexibility | Information Ordering | Memorization | Fluency of Ideas</t>
+          <t>درک کتبی | بیان شفاهی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-Mail | Freedom to Make Decisions | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Public Speaking | Spend Time Sitting | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Time Pressure | Level of Competition</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | سخنرانی عمومی | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | سطح رقابت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Anthropology and Archeology Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Communications Teachers, Postsecondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | English Language and Literature Teachers, Postsecondary | Family and Consumer Sciences Teachers, Postsecondary | Foreign Language and Literature Teachers, Postsecondary | Geography Teachers, Postsecondary | History Teachers, Postsecondary | Law Teachers, Postsecondary | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Political Science Teachers, Postsecondary | Psychology Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Social Work Teachers, Postsecondary | Sociology Teachers, Postsecondary | Teaching Assistants, Postsecondary</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان زبان و ادبیات خارجی، آموزش عالی | استادان جغرافیا، پس از متوسطه | مدرسان تاریخ، آموزش عالی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students and the community on topics such as ethics, logic, and contemporary religious thought. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write articles and books. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی و عموم مردم در موضوعاتی مانند اخلاق، منطق و اندیشه دینی معاصر. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | نگارش مقاله و کتاب. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Family and Consumer Sciences Teachers, Postsecondary (اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه)</t>
+          <t>اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه (Family and Consumer Sciences Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Assistant Professor | Associate Professor | Child Development Instructor | Dietetics Professor | Family and Consumer Sciences Professor (FCS Professor) | Food and Nutrition Professor | Human Development Professor | Instructor | Lecturer | Professor</t>
+          <t>استادیار | دانشیار | مدرس رشد کودک | استاد رژیم‌شناسی | استاد علوم خانواده و مصرف‌کننده (FCS) | استاد غذا و تغذیه | استاد رشد و تحول انسانی | مدرس | مدرس | استاد</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Blackboard Learn | Collaborative editing software | Course management system software | DOC Cop | Database management systems | Desire2Learn LMS software | Email software | Google Docs | Image scanning software | Learning management system LMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | Social computing tools | Web browser software | Zoom | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | سیستم‌های مدیریت پایگاه داده | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | Social computing tools | نرم‌افزار مرورگر وب | Zoom | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Speaking | Learning Strategies | Active Listening | Reading Comprehension | Critical Thinking | Writing | Active Learning | Monitoring</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>English Language | Education and Training | Customer and Personal Service | Psychology | Administration and Management | Mathematics | Computers and Electronics | Administrative | Sociology and Anthropology | Communications and Media | Law and Government</t>
+          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | اداری | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Written Comprehension | Oral Expression | Oral Comprehension | Written Expression | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Speech Recognition | Problem Sensitivity | Near Vision | Category Flexibility | Information Ordering | Originality | Fluency of Ideas</t>
+          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-Mail | Contact With Others | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Work With or Contribute to a Work Group or Team | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Written Letters and Memos | Spend Time Sitting | Deal With External Customers or the Public in General | Level of Competition</t>
+          <t>ایمیل | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Agricultural Sciences Teachers, Postsecondary | Business Teachers, Postsecondary | Career/Technical Education Teachers, Middle School | Career/Technical Education Teachers, Secondary School | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | Health Education Specialists | Health Specialties Teachers, Postsecondary | Instructional Coordinators | Library Science Teachers, Postsecondary | Middle School Teachers, Except Special and Career/Technical Education | Psychology Teachers, Postsecondary | Recreation and Fitness Studies Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Social Work Teachers, Postsecondary | Sociology Teachers, Postsecondary | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Secondary School</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان علوم کشاورزی، پس از متوسطه | اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | متخصصان آموزش بهداشت | استادان تخصص‌های بهداشتی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | استادان روان‌شناسی، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، متوسطه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct faculty performance evaluations. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, laboratory work, projects, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as food science, nutrition, and child care. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | ارزیابی عملکرد اعضای هیئت علمی را انجام دهید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | ارزیابی و نمره‌دهی به فعالیت کلاسی، کار آزمایشگاهی، پروژه‌ها، تکالیف و مقالات دانشجویان. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | وظایف اداری مانند خدمت به عنوان مدیر گروه را انجام دهید. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند علوم غذایی، تغذیه و مراقبت از کودک. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recreation and Fitness Studies Teachers, Postsecondary (اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه)</t>
+          <t>اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه (Recreation and Fitness Studies Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adjunct Professor | Assistant Professor | Associate Professor | Health and Human Performance Professor | Health and Physical Education Professor (HPE Professor) | Health, Physical Education, and Recreation Professor (HPER Professor) | Instructor | Kinesiology Professor | Physical Education Professor (PE Professor) | Professor</t>
+          <t>استاد مدعو | استادیار | دانشیار | استاد سلامت و عملکرد انسانی | استاد سلامت و تربیت بدنی (HPE) | استاد سلامت، تربیت بدنی و تفریحات (HPER) | مدرس | استاد حرکت‌شناسی | استاد تربیت بدنی (PE) | استاد</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Blackboard Learn | Collaborative editing software | Course management system software | DOC Cop | Dartfish ProSuite | Desire2Learn LMS software | Email software | Facebook | Google Docs | Image scanning software | Learning management system LMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Prolog | Sakai CLE | Softworks Global PESoftOne | Student record software | Web browser software | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | Dartfish ProSuite | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Facebook | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Prolog | Sakai CLE | Softworks Global PESoftOne | Student record software | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Speaking | Writing | Active Listening | Reading Comprehension | Learning Strategies | Critical Thinking | Monitoring | Active Learning</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Education and Training | English Language | Computers and Electronics | Psychology | Biology | Customer and Personal Service | Administration and Management | Mathematics | Therapy and Counseling | Communications and Media | Medicine and Dentistry</t>
+          <t>آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | درمان و مشاوره | ارتباطات و رسانه | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Fluency of Ideas | Category Flexibility | Information Ordering | Problem Sensitivity | Selective Attention | Originality</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-Mail | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | Public Speaking | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Frequency of Decision Making | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Time Pressure</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists | Biological Science Teachers, Postsecondary | Career/Technical Education Teachers, Middle School | Career/Technical Education Teachers, Postsecondary | Career/Technical Education Teachers, Secondary School | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | Environmental Science Teachers, Postsecondary | Family and Consumer Sciences Teachers, Postsecondary | Fitness and Wellness Coordinators | Health Specialties Teachers, Postsecondary | Instructional Coordinators | Nursing Instructors and Teachers, Postsecondary | Psychology Teachers, Postsecondary | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Social Work Teachers, Postsecondary | Special Education Teachers, Kindergarten | Special Education Teachers, Secondary School | Teaching Assistants, Postsecondary</t>
+          <t>متخصصان تربیت بدنی تطبیقی | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان علوم محیطی، پس از متوسطه | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان تناسب اندام و سلامتی | استادان تخصص‌های بهداشتی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مربیان و استادان پرستاری، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | مدرسان مددکاری اجتماعی، آموزش عالی | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and on career issues. | Collaborate with colleagues to address teaching and research issues. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department heads. | Plan, evaluate, and revise curricula, course content, course materials, and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as anatomy, therapeutic recreation, and conditioning theory. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Prepare students to act as sports coaches. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+          <t>به عنوان مشاور برای سازمان‌های دانشجویی عمل کنید. | دانشجویان را در مورد برنامه‌های درسی دانشگاهی و فنی و حرفه‌ای و مسائل شغلی راهنمایی کنید. | با همکاران برای رسیدگی به مسائل آموزشی و پژوهشی همکاری کنید. | کتابشناسی مواد تخصصی را برای تکالیف مطالعه خارج از کلاس تهیه کنید. | امتحانات را طراحی، اجرا و تصحیح کنید، یا این کار را به دیگران محول کنید. | در یک حوزه خاص از دانش پژوهش کنید و یافته‌ها را در مجلات تخصصی، کتاب‌ها یا رسانه‌های الکترونیکی منتشر کنید. | کارهای کلاسی، تکالیف و مقالات دانشجویان را ارزیابی و نمره‌دهی کنید. | بحث‌های کلاسی را آغاز، تسهیل و مدیریت کنید. | با خواندن ادبیات جاری، گفتگو با همکاران و شرکت در کنفرانس‌های تخصصی، از تحولات این حوزه مطلع بمانید. | ساعات اداری منظمی را برای مشاوره و کمک به دانشجویان حفظ کنید. | سوابق حضور و غیاب دانشجویان، نمرات و سایر سوابق مورد نیاز را نگهداری کنید. | در رویدادهای دانشگاهی و اجتماعی شرکت کنید. | در فعالیت‌های جذب، ثبت‌نام و کاریابی دانشجویان شرکت کنید. | انجام وظایف اداری، مانند تصدی ریاست گروه آموزشی. | برنامه‌های درسی، محتوای دوره، مواد آموزشی و روش‌های تدریس را برنامه‌ریزی، ارزیابی و بازنگری کنید. | تهیه و ارائه سخنرانی برای دانشجویان کارشناسی یا تحصیلات تکمیلی در موضوعاتی مانند تشریح، تفریحات درمانی و نظریه آمادگی جسمانی. | مواد درسی مانند سرفصل‌ها، تکالیف خانگی و جزوات را آماده کنید. | آماده‌سازی دانشجویان برای ایفای نقش مربی ورزشی. | خدمات مشاوره حرفه‌ای به دولت یا صنعت ارائه دهید. | مواد و تجهیزات مانند کتاب‌های درسی را انتخاب و تهیه کنید. | در کمیته‌های دانشگاهی یا اداری که به سیاست‌های نهادی، امور دپارتمان و مسائل دانشگاهی می‌پردازند، خدمت کنید. | بر تدریس، کارآموزی و کارهای پژوهشی دانشجویان کارشناسی یا تحصیلات تکمیلی نظارت کنید. | برای تأمین بودجه پژوهشی خارجی، پروپوزال‌های گرنت بنویسید.</t>
         </is>
       </c>
     </row>
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Career/Technical Education Teachers, Postsecondary (اساتید آموزش‌های شغلی/فنی، پس از متوسطه)</t>
+          <t>اساتید آموزش‌های شغلی/فنی، پس از متوسطه (Career/Technical Education Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Automotive Instructor | Automotive Technology Instructor | Cosmetology Instructor | Flight Instructor | HVAC-R Instructor (Heating, Ventilation, Air Conditioning, And Refrigeration Instructor) | Instructor | Professor | Teacher | Welding Instructor</t>
+          <t>مدرس فنی خودرو | مدرس فناوری خودرو | مدرس آرایشگری | مربی پرواز | مدرس تأسیسات گرمایش، تهویه، تهویه مطبوع و تبرید (HVAC-R) | مدرس | استاد | Teacher (معلم) | Welding Instructor (مربی جوشکاری)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Blackboard Learn | Blackboard software | Career management systems CMS | Collaborative editing software | Common Curriculum | Course management system software | DOC Cop | Desire2Learn LMS software | Edmodo | Email software | Google Classroom | Google Docs | GroupMe | Image scanning software | Learning management system LMS | Medical condition coding software | Medical procedure coding software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | Web browser software | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار Blackboard | سیستم‌های مدیریت شغلی CMS | نرم‌افزار ویرایش مشارکتی | Common Curriculum | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Edmodo | نرم‌افزار ایمیل | Google Classroom | Google Docs | GroupMe | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Learning Strategies | Active Listening | Reading Comprehension | Speaking | Active Learning | Critical Thinking | Writing | Monitoring</t>
+          <t>راهبردهای یادگیری | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Education and Training | English Language | Mechanical | Mathematics | Customer and Personal Service | Administrative | Engineering and Technology | Computers and Electronics | Administration and Management | Public Safety and Security | Design | Chemistry | Personnel and Human Resources | Physics</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مکانیک | ریاضیات | خدمات مشتری و شخصی | اداری | مهندسی و فناوری | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی | طراحی | شیمی | پرسنل و منابع انسانی | فیزیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Problem Sensitivity | Speech Clarity | Deductive Reasoning | Speech Recognition | Inductive Reasoning | Information Ordering | Near Vision | Selective Attention | Originality</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Contact With Others | Public Speaking | E-Mail | Indoors, Environmentally Controlled | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Being Exact or Accurate | Physical Proximity | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Spend Time Standing | Telephone Conversations | Frequency of Decision Making | Time Pressure</t>
+          <t>ارتباط با دیگران | سخنرانی عمومی | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | مکالمات تلفنی | فراوانی تصمیم‌گیری | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Automotive Engineering Technicians | Business Teachers, Postsecondary | Career/Technical Education Teachers, Middle School | Career/Technical Education Teachers, Secondary School | Computer Science Teachers, Postsecondary | Engineering Teachers, Postsecondary | Health Specialties Teachers, Postsecondary | Industrial Engineering Technologists and Technicians | Industrial Engineers | Instructional Coordinators | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Recreation and Fitness Studies Teachers, Postsecondary | Self-Enrichment Teachers | Special Education Teachers, Kindergarten | Special Education Teachers, Secondary School | Teaching Assistants, Postsecondary | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Training and Development Specialists | Tutors</t>
+          <t>تکنسین‌های مهندسی خودرو | اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | اساتید علوم رایانه، پس از متوسطه | مدرسان مهندسی، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | هماهنگ‌کنندگان آموزشی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | معلمان خودسازی | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | متخصصان آموزش و توسعه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Acquire, maintain, and repair laboratory equipment and tools. | Administer oral, written, or performance tests to measure progress and to evaluate training effectiveness. | Advise students on course selection, career decisions, and other academic and vocational concerns. | Arrange for lectures by experts in designated fields. | Conduct on-the-job training classes or training sessions to teach and demonstrate principles, techniques, procedures, or methods of designated subjects. | Determine training needs of students or workers. | Develop curricula and plan course content and methods of instruction. | Develop teaching aids, such as instructional software, multimedia visual aids, or study materials. | Integrate academic and vocational curricula so that students can obtain a variety of skills. | Observe and evaluate students' work to determine progress, provide feedback, and make suggestions for improvement. | Participate in conferences, seminars, and training sessions to keep abreast of developments in the field, and integrate relevant information into training programs. | Prepare outlines of instructional programs and training schedules and establish course goals. | Prepare reports and maintain records, such as student grades, attendance rolls, and training activity details. | Present lectures and conduct discussions to increase students' knowledge and competence using visual aids, such as graphs, charts, videotapes, and slides. | Provide individualized instruction and tutorial or remedial instruction. | Review enrollment applications and correspond with applicants to obtain additional information. | Select and assemble books, materials, supplies, and equipment for training, courses, or projects. | Serve on faculty and school committees concerned with budgeting, curriculum revision, and course and diploma requirements. | Supervise and monitor students' use of tools and equipment. | Supervise independent or group projects, field placements, laboratory work, or other training.</t>
+          <t>تهیه، نگهداری و تعمیر تجهیزات و ابزارهای آزمایشگاهی. | برگزاری آزمون‌های شفاهی، کتبی یا عملی برای سنجش پیشرفت و ارزیابی اثربخشی آموزش. | ارائه مشاوره به دانشجویان درباره انتخاب واحد، تصمیم‌های شغلی و سایر دغدغه‌های تحصیلی و حرفه‌ای. | ترتیب دادن سخنرانی متخصصان در حوزه‌های تعیین‌شده. | برگزاری کلاس‌ها یا جلسات آموزش حین کار برای تدریس و نمایش اصول، فنون، رویه‌ها یا روش‌های موضوعات تعیین‌شده. | تعیین نیازهای آموزشی دانشجویان یا کارکنان. | تدوین برنامه درسی و طراحی محتوای دروس و روش‌های تدریس. | تهیه کمک‌آموزشی‌ها، مانند نرم‌افزارهای آموزشی، کمک‌بصری‌های چندرسانه‌ای یا مواد مطالعاتی. | یکپارچه‌سازی برنامه‌های درسی نظری و حرفه‌ای تا دانشجویان بتوانند مهارت‌های گوناگون کسب کنند. | مشاهده و ارزیابی کار دانشجویان برای تعیین پیشرفت، ارائه بازخورد و پیشنهاد راه‌های بهبود. | شرکت در همایش‌ها، سمینارها و دوره‌های آموزشی برای به‌روز ماندن از تحولات حوزه و گنجاندن اطلاعات مرتبط در برنامه‌های آموزشی. | تهیه سرفصل برنامه‌های آموزشی و زمان‌بندی دوره‌ها و تعیین اهداف درس. | تهیه گزارش و نگهداری سوابق، مانند نمرات دانشجویان، فهرست حضور و غیاب و جزئیات فعالیت‌های آموزشی. | ارائه سخنرانی و اداره بحث برای افزایش دانش و شایستگی دانشجویان با استفاده از کمک‌بصری‌هایی مانند نمودار، چارت، نوار ویدئویی و اسلاید. | ارائه آموزش انفرادی و آموزش خصوصی یا جبرانی. | بازبینی درخواست‌های ثبت‌نام و مکاتبه با متقاضیان برای دریافت اطلاعات تکمیلی. | انتخاب و گردآوری کتاب‌ها، مواد، ملزومات و تجهیزات برای آموزش، دوره‌ها یا پروژه‌ها. | عضویت در کمیته‌های هیئت علمی و آموزشگاه در زمینه بودجه‌ریزی، بازنگری برنامه درسی و الزامات دروس و مدارک تحصیلی. | سرپرستی و پایش نحوه استفاده دانشجویان از ابزارها و تجهیزات. | سرپرستی پروژه‌های انفرادی یا گروهی، کارورزی میدانی، کار آزمایشگاهی یا سایر آموزش‌ها.</t>
         </is>
       </c>
     </row>
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Postsecondary Teachers, All Other (اساتید پس از متوسطه، سایر موارد)</t>
+          <t>اساتید پس از متوسطه، سایر موارد (Postsecondary Teachers, All Other)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adjunct Professor | Assistant Professor | Associate Professor | College Instructor | College Professor | Faculty Member | Lecturer | Postsecondary Instructor | University Professor | Visiting Professor</t>
+          <t>استاد مدعو | استادیار | دانشیار | مدرس دانشکده | استاد دانشکده | عضو هیئت علمی | مدرس | مدرس آموزش عالی | استاد دانشگاه | استاد مدعو</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Learning management system LMS | Blackboard software | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | Email software | Google Docs | Web browser software | Microsoft Outlook | Database software | Graphic presentation software | Microsoft Office software</t>
+          <t>سیستم مدیریت یادگیری LMS | نرم‌افزار Blackboard | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | نرم‌افزار ایمیل | Google Docs | نرم‌افزار مرورگر وب | Microsoft Outlook | نرم‌افزار پایگاه داده | نرم‌افزار ارائه گرافیکی | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Learning Strategies | Writing | Active Learning | Monitoring</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Education and Training | English Language | Communications and Media | Computers and Electronics | Psychology | Administration and Management | Mathematics | Sociology and Anthropology</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | روان‌شناسی | مدیریت و اداره | ریاضیات | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams | Public Speaking | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | E-Mail | Telephone Conversations | Spend Time Standing | Time Pressure | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Frequency of Decision Making</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Business Teachers, Postsecondary | Computer Science Teachers, Postsecondary | Education Teachers, Postsecondary | Health Specialties Teachers, Postsecondary | Communications Teachers, Postsecondary | English Language and Literature Teachers, Postsecondary | Foreign Language and Literature Teachers, Postsecondary | Art, Drama, and Music Teachers, Postsecondary | Career/Technical Education Teachers, Postsecondary | Recreation and Fitness Studies Teachers, Postsecondary | Family and Consumer Sciences Teachers, Postsecondary | Library Science Teachers, Postsecondary | Social Sciences Teachers, Postsecondary, All Other | Instructional Coordinators | Education Administrators, Postsecondary | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Self-Enrichment Teachers | Tutors | Training and Development Specialists | Educational, Guidance, and Career Counselors and Advisors</t>
+          <t>اساتید کسب‌وکار، پس از متوسطه | اساتید علوم رایانه، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | استادان تخصص‌های بهداشتی، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | مدرسان زبان و ادبیات خارجی، آموزش عالی | مدرسان هنر، نمایش و موسیقی، آموزش عالی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان علوم کتابداری، آموزش عالی | استادان علوم اجتماعی، پس از متوسطه، سایر موارد | هماهنگ‌کنندگان آموزشی | مدیران آموزشی، پس از متوسطه | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان خودسازی | معلمان خصوصی | متخصصان آموزش و توسعه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Teach postsecondary courses in subjects not classified separately. | Prepare and deliver lectures, laboratories, and studio or clinical instruction. | Develop curricula, syllabi, and instructional materials for assigned courses. | Assess student learning through assignments, examinations, and projects. | Advise and mentor students on academic and professional development. | Maintain regularly scheduled office hours for student consultation. | Conduct scholarly or applied research within the discipline. | Publish articles, books, and instructional resources. | Serve on academic committees and participate in institutional governance. | Stay current with disciplinary developments and instructional technologies. | Supervise teaching assistants, laboratory staff, and student workers. | Participate in accreditation, assessment, and program review processes. | Recruit students and represent the program at outreach events. | Collaborate with industry or community partners on applied projects.</t>
+          <t>تدریس دروس آموزش عالی در رشته‌هایی که جداگانه طبقه‌بندی نشده‌اند. | تهیه و ارائه سخنرانی، آزمایشگاه و آموزش کارگاهی یا بالینی. | تدوین برنامه درسی، سرفصل و مواد آموزشی دروس واگذارشده. | سنجش یادگیری دانشجویان از راه تکالیف، آزمون‌ها و پروژه‌ها. | ارائه مشاوره و راهنمایی به دانشجویان در زمینه رشد تحصیلی و حرفه‌ای. | برگزاری منظم ساعات حضور در دفتر برای مشاوره به دانشجویان. | انجام پژوهش علمی یا کاربردی در چارچوب رشته تخصصی. | انتشار مقالات، کتاب‌ها و منابع آموزشی. | عضویت در کمیته‌های علمی و مشارکت در اداره امور مؤسسه. | به‌روز ماندن از تحولات رشته و فناوری‌های آموزشی. | سرپرستی دستیاران آموزشی، کارکنان آزمایشگاه و دانشجویان شاغل. | مشارکت در فرایندهای اعتبارسنجی، ارزیابی و بازنگری برنامه‌های آموزشی. | جذب دانشجو و معرفی برنامه آموزشی در رویدادهای ترویجی. | همکاری با شرکای صنعتی یا اجتماعی در پروژه‌های کاربردی.</t>
         </is>
       </c>
     </row>
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Preschool Teachers, Except Special Education (مربیان پیش‌دبستانی، به استثنای آموزش استثنایی)</t>
+          <t>مربیان پیش‌دبستانی، به استثنای آموزش استثنایی (Preschool Teachers, Except Special Education)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Child Development Teacher | Early Childhood Teacher | Group Teacher | Infant Teacher | Montessori Preschool Teacher | Nursery Teacher | Pre-Kindergarten Teacher (Pre-K Teacher) | Teacher | Toddler Teacher</t>
+          <t>معلم رشد کودک | معلم دوران اولیه کودکی | معلم گروه | معلم شیرخواران | معلم پیش‌دبستانی مونته‌سوری | مربی مهدکودک | معلم پیش‌دبستانی (Pre-K) | Teacher (معلم) | معلم نوپایان</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Appletree | Bloomz | Children's educational software | ClassDojo | Common Curriculum | EasyCBM | Edmodo | Email software | Flipgrid | Google Classroom | Google Meet | Intrado SchoolMessenger | Microsoft Excel | Microsoft Office software | Microsoft Word | Nearpod | Padlet | Schoology | Seesaw | Tadpoles</t>
+          <t>Appletree | Bloomz | Children's educational software | ClassDojo | Common Curriculum | EasyCBM | Edmodo | نرم‌افزار ایمیل | Flipgrid | Google Classroom | Google Meet | Intrado SchoolMessenger | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Nearpod | Padlet | Schoology | Seesaw | Tadpoles</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Speaking | Learning Strategies | Active Listening | Critical Thinking | Monitoring | Reading Comprehension | Active Learning | Writing</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Education and Training | English Language | Public Safety and Security | Customer and Personal Service | Psychology</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Speech Clarity | Problem Sensitivity | Originality | Fluency of Ideas | Speech Recognition | Written Comprehension | Deductive Reasoning | Information Ordering | Near Vision | Written Expression | Far Vision | Inductive Reasoning</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | اصالت | روانی ایده‌ها | تشخیص گفتار | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | بینایی دور | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Contact With Others | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Frequency of Decision Making</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Career/Technical Education Teachers, Middle School | Childcare Workers | Education Administrators, Kindergarten through Secondary | Education and Childcare Administrators, Preschool and Daycare | Elementary School Teachers, Except Special Education | Instructional Coordinators | Kindergarten Teachers, Except Special Education | Middle School Teachers, Except Special and Career/Technical Education | School Psychologists | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Middle School | Special Education Teachers, Preschool | Special Education Teachers, Secondary School | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مربیان و کارکنان مراقبت از کودکان | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. | Administer tests to help determine children's developmental levels, needs, and potential. | Arrange indoor and outdoor space to facilitate creative play, motor-skill activities, and safety. | Assimilate arriving children to the school environment by greeting them, helping them remove outerwear, and selecting activities of interest to them. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. | Attend staff meetings and serve on committees as required. | Attend to children's basic needs by feeding them, dressing them, and changing their diapers. | Collaborate with other teachers and administrators in the development, evaluation, and revision of preschool programs. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. | Demonstrate activities to children. | Enforce all administration policies and rules governing students. | Establish and enforce rules for behavior and procedures for maintaining order. | Establish clear objectives for all lessons, units, and projects and communicate those objectives to children. | Identify children showing signs of emotional, developmental, or health-related problems and discuss them with supervisors, parents or guardians, and child development specialists. | Maintain accurate and complete student records as required by laws, district policies, and administrative regulations. | Meet with other professionals to discuss individual students' needs and progress. | Meet with parents and guardians to discuss their children's progress and needs, determine their priorities for their children, and suggest ways that they can promote learning and development. | Observe and evaluate children's performance, behavior, social development, and physical health. | Organize and label materials and display students' work in a manner appropriate for their ages and perceptual skills. | Organize and lead activities designed to promote physical, mental, and social development, such as games, arts and crafts, music, storytelling, and field trips. | Perform administrative duties, such as hall and cafeteria monitoring and bus loading and unloading. | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. | Plan and supervise class projects, field trips, visits by guests, or other experiential activities and guide students in learning from those activities. | Prepare and implement remedial programs for students requiring extra help. | Prepare materials and classrooms for class activities. | Prepare reports on students and activities as required by administration. | Provide a variety of materials and resources for children to explore, manipulate, and use, both in learning activities and in imaginative play. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. | Read books to entire classes or to small groups. | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. | Serve meals and snacks in accordance with nutritional guidelines. | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. | Teach basic skills, such as color, shape, number and letter recognition, personal hygiene, and social skills. | Teach proper eating habits and personal hygiene.</t>
+          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. (تطبیق روش‌های تدریس و مواد آموزشی برای برآورده کردن نیازها و علایق متغیر دانش‌آموزان.) | اجرای آزمون‌ها برای کمک به تعیین سطح رشد، نیازها و توانمندی‌های کودکان. | آماده‌سازی فضای داخلی و بیرونی برای تسهیل بازی خلاق، فعالیت‌های مهارت حرکتی و ایمنی. | همراه‌سازی کودکان تازه‌وارد با محیط مدرسه از راه خوشامدگویی، کمک به درآوردن لباس بیرونی و انتخاب فعالیت‌های مورد علاقه آنان. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. (شرکت در جلسات حرفه‌ای، کنفرانس‌های آموزشی و کارگاه‌های تربیت معلم برای حفظ و ارتقای صلاحیت حرفه‌ای.) | شرکت در جلسات کارکنان و عضویت در کمیته‌ها در صورت لزوم. | رسیدگی به نیازهای اولیه کودکان از راه غذا دادن، لباس پوشاندن و تعویض پوشک. | همکاری با سایر معلمان و مدیران در تدوین، ارزیابی و بازنگری برنامه‌های پیش‌دبستانی. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. (مشورت با سایر اعضای کارکنان برای برنامه‌ریزی و زمان‌بندی درس‌هایی که یادگیری را ارتقا می‌دهند، با پیروی از برنامه‌های درسی مصوب.) | نمایش عملی فعالیت‌ها برای کودکان. | Enforce all administration policies and rules governing students. (اجرای تمام سیاست‌ها و قوانین اداری حاکم بر دانش‌آموزان.) | وضع و اعمال قواعد رفتاری و رویه‌های حفظ نظم. | تعیین اهداف روشن برای همه درس‌ها، واحدها و پروژه‌ها و انتقال این اهداف به کودکان. | شناسایی کودکانی که نشانه‌های مشکلات عاطفی، رشدی یا سلامتی دارند و طرح آن با سرپرستان، والدین یا قیمان و متخصصان رشد کودک. | سوابق دقیق و کامل دانش‌آموزان را طبق قوانین، سیاست‌های منطقه و مقررات اداری نگهداری کنید. | Meet with other professionals to discuss individual students' needs and progress. (ملاقات با سایر متخصصان برای بحث در مورد نیازها و پیشرفت دانش‌آموزان به صورت فردی.) | دیدار با والدین و قیمان برای گفت‌وگو درباره پیشرفت و نیازهای کودکان، تعیین اولویت‌های آنان برای فرزندشان و پیشنهاد راه‌های ارتقای یادگیری و رشد. | مشاهده و ارزیابی عملکرد، رفتار، رشد اجتماعی و سلامت جسمانی کودکان. | سازماندهی و برچسب‌گذاری مواد و نمایش آثار دانش‌آموزان به شیوه‌ای متناسب با سن و مهارت‌های ادراکی آنان. | سازماندهی و راهبری فعالیت‌های طراحی‌شده برای ارتقای رشد جسمی، ذهنی و اجتماعی، مانند بازی، هنر و کاردستی، موسیقی، قصه‌گویی و بازدیدهای میدانی. | انجام وظایف اداری، مانند نظارت بر راهرو و سالن غذاخوری و سوار و پیاده کردن دانش‌آموزان از سرویس. | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. (برنامه‌ریزی و اجرای فعالیت‌ها برای یک برنامه متعادل از آموزش، نمایش و زمان کار که فرصت‌هایی را برای مشاهده، پرسش و تحقیق برای دانش‌آموزان فراهم می‌کند.) | برنامه‌ریزی و سرپرستی پروژه‌های کلاسی، بازدیدهای میدانی، حضور مهمانان یا سایر فعالیت‌های تجربی و راهنمایی دانش‌آموزان برای یادگیری از این فعالیت‌ها. | Prepare and implement remedial programs for students requiring extra help. (آماده‌سازی و اجرای برنامه‌های جبرانی برای دانش‌آموزانی که به کمک بیشتری نیاز دارند.) | Prepare materials and classrooms for class activities. (آماده‌سازی مواد و کلاس‌های درس برای فعالیت‌های کلاسی.) | Prepare reports on students and activities as required by administration. (آماده‌سازی گزارش‌ها در مورد دانش‌آموزان و فعالیت‌ها طبق الزامات مدیریت.) | فراهم کردن مواد و منابع گوناگون برای کاوش، دستکاری و استفاده کودکان، هم در فعالیت‌های یادگیری و هم در بازی خیال‌پردازانه. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. (ارائه وسایل کمکی، فناوری حمایتی و کمک به دسترسی به امکاناتی مانند سرویس‌های بهداشتی به دانش‌آموزان دارای معلولیت.) | Read books to entire classes or to small groups. (خواندن کتاب برای کل کلاس‌ها یا گروه‌های کوچک.) | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. (انتخاب، ذخیره‌سازی، سفارش، توزیع و موجودی‌گیری تجهیزات، مواد و لوازم کلاس درس.) | سرو وعده‌های غذایی و میان‌وعده‌ها مطابق دستورالعمل‌های تغذیه‌ای. | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. (نظارت، ارزیابی و برنامه‌ریزی تکالیف برای دستیاران معلم و داوطلبان.) | آموزش مهارت‌های پایه، مانند شناخت رنگ، شکل، عدد و حرف، بهداشت فردی و مهارت‌های اجتماعی. | آموزش عادات غذایی درست و بهداشت فردی.</t>
         </is>
       </c>
     </row>
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kindergarten Teachers, Except Special Education (مربیان کودکستان، به استثنای آموزش استثنایی)</t>
+          <t>مربیان کودکستان، به استثنای آموزش استثنایی (Kindergarten Teachers, Except Special Education)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bilingual Kindergarten Teacher | Classroom Teacher | Educator | Instructor | Kinder Teacher | Kindergarten Classroom Teacher | Teacher | Title One Kindergarten Teacher | Transitional Kindergarten Teacher</t>
+          <t>معلم دوزبانه کودکستان | معلم کلاس درس | آموزشگر | مدرس | معلم کودکستان | معلم کلاس کودکستان | Teacher (معلم) | معلم کودکستان طرح حمایتی | معلم کودکستان انتقالی</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bloomz | Children's educational software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | Seesaw</t>
+          <t>Bloomz | Children's educational software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | Seesaw</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monitoring | Learning Strategies | Speaking | Active Listening | Reading Comprehension | Active Learning | Critical Thinking | Writing</t>
+          <t>نظارت | راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Education and Training | English Language | Psychology | Mathematics | Customer and Personal Service | Sociology and Anthropology | Public Safety and Security | Administrative | Therapy and Counseling | Computers and Electronics | Geography</t>
+          <t>آموزش و پرورش | زبان انگلیسی | روان‌شناسی | ریاضیات | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | ایمنی و امنیت عمومی | اداری | درمان و مشاوره | رایانه و الکترونیک | جغرافیا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oral Expression | Written Comprehension | Oral Comprehension | Written Expression | Problem Sensitivity | Speech Clarity | Fluency of Ideas | Speech Recognition | Deductive Reasoning | Originality | Inductive Reasoning | Information Ordering | Selective Attention | Near Vision | Category Flexibility | Time Sharing</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | استدلال قیاسی | اصالت | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E-Mail | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Physical Proximity | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Frequency of Decision Making | Freedom to Make Decisions | Written Letters and Memos | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Determine Tasks, Priorities and Goals | Public Speaking | Time Pressure | Exposed to Disease or Infections</t>
+          <t>ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | سخنرانی عمومی | فشار زمانی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Career/Technical Education Teachers, Middle School | Education Teachers, Postsecondary | Education and Childcare Administrators, Preschool and Daycare | Elementary School Teachers, Except Special Education | Instructional Coordinators | Middle School Teachers, Except Special and Career/Technical Education | Preschool Teachers, Except Special Education | School Psychologists | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Middle School | Special Education Teachers, Preschool | Special Education Teachers, Secondary School | Substitute Teachers, Short-Term | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان علوم تربیتی، آموزش عالی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | معلمان جایگزین، کوتاه‌مدت | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Administer standardized ability and achievement tests and interpret results to determine children's developmental levels and needs. | Assimilate arriving children to the school environment by greeting them, helping them remove outerwear, and selecting activities of interest to them. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. | Attend staff meetings and serve on committees as required. | Collaborate with other teachers and administrators in the development, evaluation, and revision of kindergarten programs. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. | Confer with parents or guardians, other teachers, counselors, and administrators to resolve students' behavioral and academic problems. | Demonstrate activities to children. | Establish and enforce rules for behavior and policies and procedures to maintain order among students. | Establish clear objectives for all lessons, units, and projects and communicate those objectives to children. | Guide and counsel students with adjustment or academic problems or special academic interests. | Identify children showing signs of emotional, developmental, or health-related problems and discuss them with supervisors, parents or guardians, and child development specialists. | Instruct and monitor students in the use and care of equipment and materials to prevent injuries and damage. | Instruct students individually and in groups, adapting teaching methods to meet students' varying needs and interests. | Involve parent volunteers and older students in children's activities to facilitate involvement in focused, complex play. | Maintain accurate and complete student records and prepare reports on children and activities as required by laws, district policies, and administrative regulations. | Meet with other professionals to discuss individual students' needs and progress. | Meet with parents and guardians to discuss their children's progress and to determine their priorities for their children and their resource needs. | Observe and evaluate children's performance, behavior, social development, and physical health. | Organize and label materials and display children's work in a manner appropriate for their sizes and perceptual skills. | Organize and lead activities designed to promote physical, mental, and social development, such as games, arts and crafts, music, and storytelling. | Perform administrative duties, such as assisting in school libraries, hall and cafeteria monitoring, and bus loading and unloading. | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. | Plan and supervise class projects, field trips, visits by guests, or other experiential activities and guide students in learning from those activities. | Prepare and implement remedial programs for students requiring extra help. | Prepare children for later grades by encouraging them to explore learning opportunities and to persevere with challenging tasks. | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. | Prepare materials, classrooms, and other indoor and outdoor spaces to facilitate creative play, learning and motor-skill activities, and safety. | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. | Prepare, administer, and grade tests and assignments to evaluate children's progress. | Provide a variety of materials and resources for children to explore, manipulate, and use, both in learning activities and in imaginative play. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. | Read books to entire classes or to small groups. | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. | Teach basic skills, such as color, shape, number and letter recognition, personal hygiene, and social skills. | Use computers, audio-visual aids, and other equipment and materials to supplement presentations.</t>
+          <t>اجرای آزمون‌های استاندارد توانایی و پیشرفت تحصیلی و تفسیر نتایج برای تعیین سطح رشد و نیازهای کودکان. | همراه‌سازی کودکان تازه‌وارد با محیط مدرسه از راه خوشامدگویی، کمک به درآوردن لباس بیرونی و انتخاب فعالیت‌های مورد علاقه آنان. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. (شرکت در جلسات حرفه‌ای، کنفرانس‌های آموزشی و کارگاه‌های تربیت معلم برای حفظ و ارتقای صلاحیت حرفه‌ای.) | شرکت در جلسات کارکنان و عضویت در کمیته‌ها در صورت لزوم. | همکاری با سایر معلمان و مدیران در تدوین، ارزیابی و بازنگری برنامه‌های کودکستان. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. (مشورت با سایر اعضای کارکنان برای برنامه‌ریزی و زمان‌بندی درس‌هایی که یادگیری را ارتقا می‌دهند، با پیروی از برنامه‌های درسی مصوب.) | Confer with parents or guardians, other teachers, counselors, and administrators to resolve students' behavioral and academic problems. (مشورت با والدین یا سرپرستان، سایر معلمان، مشاوران و مدیران برای حل مشکلات رفتاری و تحصیلی دانش‌آموزان.) | نمایش عملی فعالیت‌ها برای کودکان. | Establish and enforce rules for behavior and policies and procedures to maintain order among students. (ایجاد و اجرای قوانین رفتاری و سیاست‌ها و رویه‌های حفظ نظم در میان دانش‌آموزان.) | تعیین اهداف روشن برای همه درس‌ها، واحدها و پروژه‌ها و انتقال این اهداف به کودکان. | Guide and counsel students with adjustment or academic problems or special academic interests. (راهنمایی و مشاوره به دانش‌آموزان در خصوص مشکلات سازگاری یا تحصیلی یا علایق تحصیلی خاص.) | شناسایی کودکانی که نشانه‌های مشکلات عاطفی، رشدی یا سلامتی دارند و طرح آن با سرپرستان، والدین یا قیمان و متخصصان رشد کودک. | Instruct and monitor students in the use and care of equipment and materials to prevent injuries and damage. (آموزش و نظارت بر دانش‌آموزان در استفاده و مراقبت از تجهیزات و مواد برای جلوگیری از آسیب و خسارت.) | آموزش دانش‌آموزان به‌صورت انفرادی و گروهی، با تطبیق روش‌های تدریس بر نیازها و علایق متفاوت آنان. | مشارکت دادن والدین داوطلب و دانش‌آموزان بزرگ‌تر در فعالیت‌های کودکان برای تسهیل درگیر شدن آنان در بازی متمرکز و پیچیده. | نگهداری سوابق دقیق و کامل دانش‌آموزان و تهیه گزارش درباره کودکان و فعالیت‌ها، مطابق الزامات قوانین، سیاست‌های منطقه و مقررات اداری. | Meet with other professionals to discuss individual students' needs and progress. (ملاقات با سایر متخصصان برای بحث در مورد نیازها و پیشرفت دانش‌آموزان به صورت فردی.) | دیدار با والدین و قیمان برای گفت‌وگو درباره پیشرفت کودکان و تعیین اولویت‌های آنان برای فرزندشان و نیازهای منابعی ایشان. | مشاهده و ارزیابی عملکرد، رفتار، رشد اجتماعی و سلامت جسمانی کودکان. | سازماندهی و برچسب‌گذاری مواد و نمایش آثار کودکان به شیوه‌ای متناسب با قد و مهارت‌های ادراکی آنان. | سازماندهی و راهبری فعالیت‌های طراحی‌شده برای ارتقای رشد جسمی، ذهنی و اجتماعی، مانند بازی، هنر و کاردستی، موسیقی و قصه‌گویی. | انجام وظایف اداری، مانند کمک در کتابخانه مدرسه، نظارت بر راهرو و سالن غذاخوری و سوار و پیاده کردن دانش‌آموزان از سرویس. | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. (برنامه‌ریزی و اجرای فعالیت‌ها برای یک برنامه متعادل از آموزش، نمایش و زمان کار که فرصت‌هایی را برای مشاهده، پرسش و تحقیق برای دانش‌آموزان فراهم می‌کند.) | برنامه‌ریزی و سرپرستی پروژه‌های کلاسی، بازدیدهای میدانی، حضور مهمانان یا سایر فعالیت‌های تجربی و راهنمایی دانش‌آموزان برای یادگیری از این فعالیت‌ها. | Prepare and implement remedial programs for students requiring extra help. (آماده‌سازی و اجرای برنامه‌های جبرانی برای دانش‌آموزانی که به کمک بیشتری نیاز دارند.) | آماده‌سازی کودکان برای پایه‌های بالاتر از راه تشویق آنان به کاوش در فرصت‌های یادگیری و پشتکار در تکالیف چالش‌برانگیز. | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. (آماده‌سازی برای کلاس‌های محول‌شده و ارائه شواهد کتبی از آمادگی در صورت درخواست سرپرستان مستقیم.) | آماده‌سازی مواد، کلاس‌ها و سایر فضاهای داخلی و بیرونی برای تسهیل بازی خلاق، یادگیری، فعالیت‌های مهارت حرکتی و ایمنی. | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. (آماده‌سازی اهداف و رئوس مطالب برای دوره‌های تحصیلی، با پیروی از دستورالعمل‌های برنامه درسی یا الزامات ایالت‌ها و مدارس.) | تهیه، اجرا و نمره‌دهی آزمون‌ها و تکالیف برای ارزیابی پیشرفت کودکان. | فراهم کردن مواد و منابع گوناگون برای کاوش، دستکاری و استفاده کودکان، هم در فعالیت‌های یادگیری و هم در بازی خیال‌پردازانه. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. (ارائه وسایل کمکی، فناوری حمایتی و کمک به دسترسی به امکاناتی مانند سرویس‌های بهداشتی به دانش‌آموزان دارای معلولیت.) | Read books to entire classes or to small groups. (خواندن کتاب برای کل کلاس‌ها یا گروه‌های کوچک.) | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. (انتخاب، ذخیره‌سازی، سفارش، توزیع و موجودی‌گیری تجهیزات، مواد و لوازم کلاس درس.) | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. (نظارت، ارزیابی و برنامه‌ریزی تکالیف برای دستیاران معلم و داوطلبان.) | آموزش مهارت‌های پایه، مانند شناخت رنگ، شکل، عدد و حرف، بهداشت فردی و مهارت‌های اجتماعی. | Use computers, audio-visual aids, and other equipment and materials to supplement presentations. (استفاده از کامپیوتر، وسایل کمک آموزشی دیداری-شنیداری و سایر تجهیزات و مواد برای تکمیل ارائه‌ها.)</t>
         </is>
       </c>
     </row>
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش استثنایی)</t>
+          <t>معلمان دبستان، به استثنای آموزش استثنایی (Elementary School Teachers, Except Special Education)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Art Teacher | Classroom Teacher | Elementary Classroom Teacher | Elementary School Teacher | Elementary Teacher | Math Teacher (Mathematics Teacher) | Music Teacher | Primary Teacher | Reading Teacher | Teacher</t>
+          <t>Art Teacher (معلم هنر) | معلم کلاس درس | معلم کلاس ابتدایی | معلم مدرسه ابتدایی | معلم ابتدایی | Math Teacher (Mathematics Teacher) (معلم ریاضی) | Music Teacher (معلم موسیقی) | معلم ابتدایی | معلم خواندن | Teacher (معلم)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Blackboard software | Children's educational software | ClassDojo | ClassTag | Common Curriculum | EasyCBM | Edpuzzle | Email software | Flipgrid | Google Classroom | Google Docs | Google Drive | Google Meet | Graphics software | JamBoard | Kahoot! | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Nearpod | Padlet | Pear Deck | Schoology | Screencastify | Seesaw | Tadpoles | Web browser software</t>
+          <t>نرم‌افزار Blackboard | Children's educational software | ClassDojo | ClassTag | Common Curriculum | EasyCBM | Edpuzzle | نرم‌افزار ایمیل | Flipgrid | Google Classroom | Google Docs | Google Drive | Google Meet | نرم‌افزار گرافیکی | JamBoard | Kahoot! | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Nearpod | Padlet | Pear Deck | Schoology | Screencastify | Seesaw | Tadpoles | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Learning Strategies | Speaking | Active Listening | Monitoring | Critical Thinking | Reading Comprehension | Writing | Active Learning</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>English Language | Education and Training | Mathematics | Customer and Personal Service | Psychology | Therapy and Counseling | Computers and Electronics | Public Safety and Security | Administrative | Administration and Management | Communications and Media</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | رایانه و الکترونیک | ایمنی و امنیت عمومی | اداری | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Problem Sensitivity | Inductive Reasoning | Speech Recognition | Speech Clarity | Written Comprehension | Written Expression | Fluency of Ideas | Deductive Reasoning | Information Ordering | Near Vision | Originality | Category Flexibility | Selective Attention | Far Vision | Time Sharing | Flexibility of Closure | Mathematical Reasoning</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | اصالت | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | تقسیم توجه | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-Mail | Work With or Contribute to a Work Group or Team | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Public Speaking | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Conflict Situations | Dealing With Unpleasant, Angry, or Discourteous People | Freedom to Make Decisions | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Time Pressure | Written Letters and Memos | Telephone Conversations</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Art, Drama, and Music Teachers, Postsecondary | Career/Technical Education Teachers, Middle School | Education Administrators, Kindergarten through Secondary | Education Teachers, Postsecondary | Instructional Coordinators | Kindergarten Teachers, Except Special Education | Middle School Teachers, Except Special and Career/Technical Education | Preschool Teachers, Except Special Education | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Middle School | Special Education Teachers, Preschool | Special Education Teachers, Secondary School | Teaching Assistants, Postsecondary | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان هنر، نمایش و موسیقی، آموزش عالی | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. | Administer standardized ability and achievement tests, and interpret results to determine student strengths and needs. | Assign and grade class work and homework. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. | Attend staff meetings and serve on committees, as required. | Collaborate with other teachers and administrators in the development, evaluation, and revision of elementary school programs. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. | Confer with parents or guardians, teachers, counselors, and administrators to resolve students' behavioral and academic problems. | Enforce administration policies and rules governing students. | Establish and enforce rules for behavior and procedures for maintaining order among the students. | Establish clear objectives for all lessons, units, and projects and communicate those objectives to students. | Guide and counsel students with adjustment or academic problems or with special academic interests. | Instruct and monitor students in the use and care of equipment and materials to prevent injuries and damage. | Instruct students individually and in groups, using teaching methods such as lectures, discussions, and demonstrations. | Involve parent volunteers and older students in children's activities to facilitate involvement in focused, complex play. | Maintain accurate and complete student records as required by laws, district policies, and administrative regulations. | Meet with other professionals to discuss individual students' needs and progress. | Meet with parents and guardians to discuss their children's progress and to determine priorities for their children and their resource needs. | Observe and evaluate students' performance, behavior, social development, and physical health. | Organize and label materials and display students' work. | Organize and lead activities designed to promote physical, mental, and social development, such as games, arts and crafts, music, and storytelling. | Perform administrative duties, such as school library assistance, hall and cafeteria monitoring, and bus loading and unloading. | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. | Plan and supervise class projects, field trips, visits by guest speakers or other experiential activities, and guide students in learning from those activities. | Prepare and implement remedial programs for students requiring extra help. | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. | Prepare materials and classrooms for class activities. | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. | Prepare reports on students and activities as required by administration. | Prepare students for later grades by encouraging them to explore learning opportunities and to persevere with challenging tasks. | Prepare, administer, and grade tests and assignments to evaluate students' progress. | Provide a variety of materials and resources for children to explore, manipulate, and use, both in learning activities and in imaginative play. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. | Read books to entire classes or small groups. | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. | Sponsor extracurricular activities, such as clubs, student organizations, and academic contests. | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. | Use computers, audio-visual aids, and other equipment and materials to supplement presentations.</t>
+          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. (تطبیق روش‌های تدریس و مواد آموزشی برای برآورده کردن نیازها و علایق متغیر دانش‌آموزان.) | اجرای آزمون‌های استاندارد توانایی و پیشرفت تحصیلی و تفسیر نتایج برای تعیین نقاط قوت و نیازهای دانش‌آموزان. | Assign and grade class work and homework. (تعیین و نمره‌دهی به تکالیف کلاسی و خانگی.) | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. (شرکت در جلسات حرفه‌ای، کنفرانس‌های آموزشی و کارگاه‌های تربیت معلم برای حفظ و ارتقای صلاحیت حرفه‌ای.) | Attend staff meetings and serve on committees, as required. (شرکت در جلسات کارکنان و عضویت در کمیته‌ها، در صورت نیاز.) | همکاری با سایر معلمان و مدیران در تدوین، ارزیابی و بازنگری برنامه‌های مدرسه ابتدایی. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. (مشورت با سایر اعضای کارکنان برای برنامه‌ریزی و زمان‌بندی درس‌هایی که یادگیری را ارتقا می‌دهند، با پیروی از برنامه‌های درسی مصوب.) | رایزنی با والدین یا قیمان، معلمان، مشاوران و مدیران برای رفع مشکلات رفتاری و تحصیلی دانش‌آموزان. | اجرای سیاست‌ها و قوانین اداری حاکم بر دانش‌آموزان. | وضع و اعمال قواعد رفتاری و رویه‌های حفظ نظم میان دانش‌آموزان. | Establish clear objectives for all lessons, units, and projects and communicate those objectives to students. (تعیین اهداف روشن برای تمام درس‌ها، واحدها و پروژه‌ها و ابلاغ آن اهداف به دانش‌آموزان.) | راهنمایی و مشاوره به دانش‌آموزان دارای مشکلات سازگاری یا تحصیلی یا علایق تحصیلی ویژه. | Instruct and monitor students in the use and care of equipment and materials to prevent injuries and damage. (آموزش و نظارت بر دانش‌آموزان در استفاده و مراقبت از تجهیزات و مواد برای جلوگیری از آسیب و خسارت.) | آموزش دانش‌آموزان به‌صورت انفرادی و گروهی، با روش‌های تدریسی مانند سخنرانی، بحث و نمایش عملی. | مشارکت دادن والدین داوطلب و دانش‌آموزان بزرگ‌تر در فعالیت‌های کودکان برای تسهیل درگیر شدن آنان در بازی متمرکز و پیچیده. | سوابق دقیق و کامل دانش‌آموزان را طبق قوانین، سیاست‌های منطقه و مقررات اداری نگهداری کنید. | Meet with other professionals to discuss individual students' needs and progress. (ملاقات با سایر متخصصان برای بحث در مورد نیازها و پیشرفت دانش‌آموزان به صورت فردی.) | Meet with parents and guardians to discuss their children's progress and to determine priorities for their children and their resource needs. (ملاقات با والدین و سرپرستان برای بحث در مورد پیشرفت فرزندانشان و تعیین اولویت‌ها برای فرزندان و نیازهای منابع آن‌ها.) | Observe and evaluate students' performance, behavior, social development, and physical health. (مشاهده و ارزیابی عملکرد، رفتار، رشد اجتماعی و سلامت جسمانی دانش‌آموزان.) | Organize and label materials and display students' work. (سازماندهی و برچسب‌گذاری مواد و نمایش کارهای دانش‌آموزان.) | سازماندهی و راهبری فعالیت‌های طراحی‌شده برای ارتقای رشد جسمی، ذهنی و اجتماعی، مانند بازی، هنر و کاردستی، موسیقی و قصه‌گویی. | Perform administrative duties, such as school library assistance, hall and cafeteria monitoring, and bus loading and unloading. (انجام وظایف اداری، مانند کمک به کتابخانه مدرسه، نظارت بر سالن و کافه‌تریا، و سوار و پیاده کردن اتوبوس.) | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. (برنامه‌ریزی و اجرای فعالیت‌ها برای یک برنامه متعادل از آموزش، نمایش و زمان کار که فرصت‌هایی را برای مشاهده، پرسش و تحقیق برای دانش‌آموزان فراهم می‌کند.) | Plan and supervise class projects, field trips, visits by guest speakers or other experiential activities, and guide students in learning from those activities. (برنامه‌ریزی و نظارت بر پروژه‌های کلاسی، اردوهای علمی، بازدید سخنرانان مهمان یا سایر فعالیت‌های تجربی، و راهنمایی دانش‌آموزان در یادگیری از آن فعالیت‌ها.) | Prepare and implement remedial programs for students requiring extra help. (آماده‌سازی و اجرای برنامه‌های جبرانی برای دانش‌آموزانی که به کمک بیشتری نیاز دارند.) | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. (آماده‌سازی برای کلاس‌های محول‌شده و ارائه شواهد کتبی از آمادگی در صورت درخواست سرپرستان مستقیم.) | Prepare materials and classrooms for class activities. (آماده‌سازی مواد و کلاس‌های درس برای فعالیت‌های کلاسی.) | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. (آماده‌سازی اهداف و رئوس مطالب برای دوره‌های تحصیلی، با پیروی از دستورالعمل‌های برنامه درسی یا الزامات ایالت‌ها و مدارس.) | Prepare reports on students and activities as required by administration. (آماده‌سازی گزارش‌ها در مورد دانش‌آموزان و فعالیت‌ها طبق الزامات مدیریت.) | Prepare students for later grades by encouraging them to explore learning opportunities and to persevere with challenging tasks. (آماده‌سازی دانش‌آموزان برای پایه‌های بالاتر با تشویق آن‌ها به کشف فرصت‌های یادگیری و استقامت در انجام تکالیف چالش‌برانگیز.) | Prepare, administer, and grade tests and assignments to evaluate students' progress. (آماده‌سازی، اجرا و نمره‌دهی به آزمون‌ها و تکالیف برای ارزیابی پیشرفت دانش‌آموزان.) | فراهم کردن مواد و منابع گوناگون برای کاوش، دستکاری و استفاده کودکان، هم در فعالیت‌های یادگیری و هم در بازی خیال‌پردازانه. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. (ارائه وسایل کمکی، فناوری حمایتی و کمک به دسترسی به امکاناتی مانند سرویس‌های بهداشتی به دانش‌آموزان دارای معلولیت.) | کتاب‌خوانی برای کل کلاس یا گروه‌های کوچک. | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. (انتخاب، ذخیره‌سازی، سفارش، توزیع و موجودی‌گیری تجهیزات، مواد و لوازم کلاس درس.) | Sponsor extracurricular activities, such as clubs, student organizations, and academic contests. (حمایت از فعالیت‌های فوق‌برنامه، مانند باشگاه‌ها، سازمان‌های دانش‌آموزی و مسابقات علمی.) | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. (نظارت، ارزیابی و برنامه‌ریزی تکالیف برای دستیاران معلم و داوطلبان.) | Use computers, audio-visual aids, and other equipment and materials to supplement presentations. (استفاده از کامپیوتر، وسایل کمک آموزشی دیداری-شنیداری و سایر تجهیزات و مواد برای تکمیل ارائه‌ها.)</t>
         </is>
       </c>
     </row>
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Middle School Teachers, Except Special and Career/Technical Education (معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای)</t>
+          <t>معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای (Middle School Teachers, Except Special and Career/Technical Education)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Art Teacher | English Teacher | Language Arts Teacher (LA Teacher) | Math Teacher (Mathematics Teacher) | Middle School Teacher | Music Teacher | PE Teacher (Physical Education Teacher) | Science Teacher | Social Studies Teacher | Teacher</t>
+          <t>Art Teacher (معلم هنر) | English Teacher (معلم انگلیسی) | معلم ادبیات و زبان (LA Teacher) | Math Teacher (Mathematics Teacher) (معلم ریاضی) | معلم دوره متوسطه اول | Music Teacher (معلم موسیقی) | PE Teacher (Physical Education Teacher) (معلم تربیت بدنی) | Science Teacher (معلم علوم) | Social Studies Teacher (معلم مطالعات اجتماعی) | Teacher (معلم)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apple Final Cut Pro | Apple macOS | Appletree | Blackboard software | Children's educational software | ClassTag | Common Curriculum | Desmos | Edmodo | Email software | Facebook | Flipgrid | Google Classroom | Google Docs | Google Drive | Google Meet | JamBoard | Kahoot! | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Moodle | Nearpod | Padlet | Pear Deck | Schoology | Screencastify | Seesaw | Tadpoles | Video editing software | Web browser software | Zoom</t>
+          <t>Apple Final Cut Pro | Apple macOS | Appletree | نرم‌افزار Blackboard | Children's educational software | ClassTag | Common Curriculum | Desmos | Edmodo | نرم‌افزار ایمیل | Facebook | Flipgrid | Google Classroom | Google Docs | Google Drive | Google Meet | JamBoard | Kahoot! | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Moodle | Nearpod | Padlet | Pear Deck | Schoology | Screencastify | Seesaw | Tadpoles | نرم‌افزار ویرایش ویدیو | نرم‌افزار مرورگر وب | Zoom</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Learning Strategies | Speaking | Active Listening | Reading Comprehension | Writing | Active Learning | Monitoring | Critical Thinking</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Education and Training | English Language | Philosophy and Theology | Mathematics | Psychology | Computers and Electronics | History and Archeology | Public Safety and Security | Customer and Personal Service | Sociology and Anthropology | Administrative | Geography</t>
+          <t>آموزش و پرورش | زبان انگلیسی | فلسفه و الهیات | ریاضیات | روان‌شناسی | رایانه و الکترونیک | تاریخ و باستان‌شناسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | اداری | جغرافیا</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Problem Sensitivity | Information Ordering | Speech Clarity | Deductive Reasoning | Near Vision | Speech Recognition | Fluency of Ideas | Inductive Reasoning | Originality | Selective Attention | Flexibility of Closure | Memorization</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | استدلال استقرایی | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Freedom to Make Decisions | Physical Proximity | Frequency of Decision Making | Public Speaking | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Standing</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | سخنرانی عمومی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Art, Drama, and Music Teachers, Postsecondary | Career/Technical Education Teachers, Middle School | Education Administrators, Kindergarten through Secondary | Education Teachers, Postsecondary | Elementary School Teachers, Except Special Education | English Language and Literature Teachers, Postsecondary | Instructional Coordinators | Kindergarten Teachers, Except Special Education | Secondary School Teachers, Except Special and Career/Technical Education | Self-Enrichment Teachers | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Middle School | Special Education Teachers, Preschool | Special Education Teachers, Secondary School | Teaching Assistants, Postsecondary | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان هنر، نمایش و موسیقی، آموزش عالی | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. | Administer standardized ability and achievement tests, and interpret results to determine student strengths and needs. | Assign lessons and correct homework. | Assist students who need extra help, such as by tutoring and preparing and implementing remedial programs. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. | Attend staff meetings and serve on staff committees, as required. | Collaborate with other teachers and administrators in the development, evaluation, and revision of middle school programs. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. | Confer with parents or guardians, other teachers, counselors, and administrators to resolve students' behavioral and academic problems. | Coordinate and supervise extracurricular activities, such as clubs, student organizations, and academic contests. | Enforce all administration policies and rules governing students. | Establish and enforce rules for behavior and procedures for maintaining order among students. | Establish clear objectives for all lessons, units, and projects, and communicate these objectives to students. | Guide and counsel students with adjustment or academic problems, or special academic interests. | Instruct and monitor students in the use and care of equipment and materials to prevent injury and damage. | Instruct through lectures, discussions, and demonstrations in one or more subjects, such as English, mathematics, or social studies. | Maintain accurate, complete, and correct student records as required by laws, district policies, and administrative regulations. | Meet or correspond with parents or guardians to discuss children's progress and to determine priorities and resource needs. | Meet with other professionals to discuss individual students' needs and progress. | Observe and evaluate students' performance, behavior, social development, and physical health. | Organize and label materials and display students' work. | Organize and supervise games and other recreational activities to promote physical, mental, and social development. | Perform administrative duties, such as school library assistance, hall and cafeteria monitoring, and bus loading and unloading. | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. | Plan and supervise class projects, field trips, visits by guest speakers, or other experiential activities, and guide students in learning from such activities. | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. | Prepare materials and classrooms for class activities. | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. | Prepare reports on students and activities as required by administration. | Prepare students for later grades by encouraging them to explore learning opportunities and to persevere with challenging tasks. | Prepare, administer, and grade tests and assignments to evaluate students' progress. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. | Use computers, audio-visual aids, and other equipment and materials to supplement presentations.</t>
+          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. (تطبیق روش‌های تدریس و مواد آموزشی برای برآورده کردن نیازها و علایق متغیر دانش‌آموزان.) | اجرای آزمون‌های استاندارد توانایی و پیشرفت تحصیلی و تفسیر نتایج برای تعیین نقاط قوت و نیازهای دانش‌آموزان. | تعیین درس و تصحیح تکالیف. | کمک به دانش‌آموزانی که به یاری بیشتری نیاز دارند، مانند آموزش خصوصی و تهیه و اجرای برنامه‌های جبرانی. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. (شرکت در جلسات حرفه‌ای، کنفرانس‌های آموزشی و کارگاه‌های تربیت معلم برای حفظ و ارتقای صلاحیت حرفه‌ای.) | شرکت در جلسات کارکنان و عضویت در کمیته‌های کارکنان، در صورت لزوم. | همکاری با سایر معلمان و مدیران در تدوین، ارزیابی و بازنگری برنامه‌های دوره متوسطه اول. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. (مشورت با سایر اعضای کارکنان برای برنامه‌ریزی و زمان‌بندی درس‌هایی که یادگیری را ارتقا می‌دهند، با پیروی از برنامه‌های درسی مصوب.) | Confer with parents or guardians, other teachers, counselors, and administrators to resolve students' behavioral and academic problems. (مشورت با والدین یا سرپرستان، سایر معلمان، مشاوران و مدیران برای حل مشکلات رفتاری و تحصیلی دانش‌آموزان.) | هماهنگی و سرپرستی فعالیت‌های فوق‌برنامه، مانند انجمن‌ها، تشکل‌های دانش‌آموزی و مسابقات علمی. | Enforce all administration policies and rules governing students. (اجرای تمام سیاست‌ها و قوانین اداری حاکم بر دانش‌آموزان.) | Establish and enforce rules for behavior and procedures for maintaining order among students. (ایجاد و اجرای قوانین رفتاری و رویه‌های حفظ نظم در میان دانش‌آموزان.) | تعیین اهداف روشن برای همه درس‌ها، واحدها و پروژه‌ها و انتقال این اهداف به دانش‌آموزان. | راهنمایی و مشاوره به دانش‌آموزان دارای مشکلات سازگاری یا تحصیلی، یا علایق تحصیلی ویژه. | Instruct and monitor students in the use and care of equipment and materials to prevent injury and damage. (آموزش و نظارت بر دانش‌آموزان در استفاده و مراقبت از تجهیزات و مواد برای جلوگیری از آسیب و خسارت.) | Instruct through lectures, discussions, and demonstrations in one or more subjects, such as English, mathematics, or social studies. (تدریس از طریق سخنرانی، بحث و نمایش در یک یا چند موضوع، مانند انگلیسی، ریاضیات یا مطالعات اجتماعی.) | نگهداری سوابق دقیق، کامل و صحیح دانش‌آموزان، مطابق الزامات قوانین، سیاست‌های منطقه و مقررات اداری. | دیدار یا مکاتبه با والدین یا قیمان برای گفت‌وگو درباره پیشرفت کودکان و تعیین اولویت‌ها و نیازهای منابعی. | Meet with other professionals to discuss individual students' needs and progress. (ملاقات با سایر متخصصان برای بحث در مورد نیازها و پیشرفت دانش‌آموزان به صورت فردی.) | Observe and evaluate students' performance, behavior, social development, and physical health. (مشاهده و ارزیابی عملکرد، رفتار، رشد اجتماعی و سلامت جسمانی دانش‌آموزان.) | Organize and label materials and display students' work. (سازماندهی و برچسب‌گذاری مواد و نمایش کارهای دانش‌آموزان.) | سازماندهی و نظارت بر بازی‌ها و سایر فعالیت‌های تفریحی برای ارتقای رشد جسمی، ذهنی و اجتماعی. | Perform administrative duties, such as school library assistance, hall and cafeteria monitoring, and bus loading and unloading. (انجام وظایف اداری، مانند کمک به کتابخانه مدرسه، نظارت بر سالن و کافه‌تریا، و سوار و پیاده کردن اتوبوس.) | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. (برنامه‌ریزی و اجرای فعالیت‌ها برای یک برنامه متعادل از آموزش، نمایش و زمان کار که فرصت‌هایی را برای مشاهده، پرسش و تحقیق برای دانش‌آموزان فراهم می‌کند.) | برنامه‌ریزی و سرپرستی پروژه‌های کلاسی، بازدیدهای میدانی، حضور سخنرانان مهمان یا سایر فعالیت‌های تجربی و راهنمایی دانش‌آموزان برای یادگیری از این فعالیت‌ها. | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. (آماده‌سازی برای کلاس‌های محول‌شده و ارائه شواهد کتبی از آمادگی در صورت درخواست سرپرستان مستقیم.) | Prepare materials and classrooms for class activities. (آماده‌سازی مواد و کلاس‌های درس برای فعالیت‌های کلاسی.) | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. (آماده‌سازی اهداف و رئوس مطالب برای دوره‌های تحصیلی، با پیروی از دستورالعمل‌های برنامه درسی یا الزامات ایالت‌ها و مدارس.) | Prepare reports on students and activities as required by administration. (آماده‌سازی گزارش‌ها در مورد دانش‌آموزان و فعالیت‌ها طبق الزامات مدیریت.) | Prepare students for later grades by encouraging them to explore learning opportunities and to persevere with challenging tasks. (آماده‌سازی دانش‌آموزان برای پایه‌های بالاتر با تشویق آن‌ها به کشف فرصت‌های یادگیری و استقامت در انجام تکالیف چالش‌برانگیز.) | Prepare, administer, and grade tests and assignments to evaluate students' progress. (آماده‌سازی، اجرا و نمره‌دهی به آزمون‌ها و تکالیف برای ارزیابی پیشرفت دانش‌آموزان.) | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. (ارائه وسایل کمکی، فناوری حمایتی و کمک به دسترسی به امکاناتی مانند سرویس‌های بهداشتی به دانش‌آموزان دارای معلولیت.) | Select, store, order, issue, and inventory classroom equipment, materials, and supplies. (انتخاب، ذخیره‌سازی، سفارش، توزیع و موجودی‌گیری تجهیزات، مواد و لوازم کلاس درس.) | Supervise, evaluate, and plan assignments for teacher assistants and volunteers. (نظارت، ارزیابی و برنامه‌ریزی تکالیف برای دستیاران معلم و داوطلبان.) | Use computers, audio-visual aids, and other equipment and materials to supplement presentations. (استفاده از کامپیوتر، وسایل کمک آموزشی دیداری-شنیداری و سایر تجهیزات و مواد برای تکمیل ارائه‌ها.)</t>
         </is>
       </c>
     </row>
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Career/Technical Education Teachers, Middle School (معلمان آموزش‌های شغلی/فنی، دوره راهنمایی)</t>
+          <t>معلمان آموزش‌های شغلی/فنی، دوره راهنمایی (Career/Technical Education Teachers, Middle School)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Business Education Teacher | Business Teacher | Career and Technology Education Teacher (CTE Teacher) | Computer Teacher | Family and Consumer Sciences Teacher (FACS Teacher) | Industrial Arts Teacher | Industrial Technology Teacher | Teacher | Technology Education Teacher (Tech Ed Teacher) | Technology Teacher</t>
+          <t>معلم آموزش بازرگانی | معلم بازرگانی | معلم آموزش حرفه‌ای و فناوری (CTE) | معلم رایانه | Family and Consumer Sciences Teacher (FACS Teacher) (معلم علوم خانواده و مصرف‌کننده) | معلم هنرهای صنعتی | معلم فناوری صنعتی | Teacher (معلم) | معلم آموزش فناوری (Tech Ed Teacher) | معلم فناوری</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | Amazon Web Services AWS software | Ansible software | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache JMeter | Apache Kafka | Apache Tomcat | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Bash | Blackboard Learn | C# | C++ | Collaborative editing software | Course management system software | DOC Cop | Data visualization software | Debugging software | Desire2Learn LMS software | Docker | Eclipse IDE | Elasticsearch | Email software | Extensible markup language XML | Git | GitHub | Go | Google Angular | Google Docs | Hypertext markup language HTML | Hypertext preprocessor PHP | Image scanning software | JUnit | JavaScript | JavaScript Object Notation JSON | Jenkins CI | Learning management system LMS | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Azure software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | MongoDB | MySQL | NoSQL | Node.js | Object oriented development environment software | Objective C | Oracle Database | Oracle Java | Oracle PeopleSoft | Perl | PostgreSQL | Puppet | Python | React | Red Hat Enterprise Linux | Ruby | SAP software | SAS | Sakai CLE | Salesforce Visualforce | Salesforce software | Scala | Selenium | Shell script | Splunk Enterprise | Spring Boot | Structured query language SQL | Tableau | TestNG | UNIX | VMware | Web browser software | iParadigms Turnitin | jQuery</t>
+          <t>Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache JMeter | Apache Kafka | Apache Tomcat | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Bash | Blackboard Learn | C# | C++ | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار تجسم داده | نرم‌افزار عیب‌یابی | نرم‌افزار Desire2Learn LMS | Docker | Eclipse IDE | Elasticsearch | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | Git | GitHub | Go | Google Angular | Google Docs | زبان نشانه‌گذاری ابرمتن HTML | Hypertext preprocessor PHP | نرم‌افزار اسکن تصویر | JUnit | JavaScript | JavaScript Object Notation JSON | Jenkins CI | سیستم مدیریت یادگیری LMS | Linux | Microsoft .NET Framework | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | MongoDB | MySQL | NoSQL | Node.js | نرم‌افزار محیط توسعه شیءگرا | Objective C | Oracle Database | Oracle Java | Oracle PeopleSoft | Perl | PostgreSQL | Puppet | Python | React | Red Hat Enterprise Linux | Ruby | نرم‌افزار SAP | SAS | Sakai CLE | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Selenium | Shell script | Splunk Enterprise | Spring Boot | زبان پرس‌وجوی ساختاریافته SQL | Tableau | TestNG | UNIX | VMware | نرم‌افزار مرورگر وب | iParadigms Turnitin | jQuery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Learning Strategies | Critical Thinking | Monitoring | Writing | Active Learning</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>English Language | Education and Training | Psychology | Computers and Electronics | Administrative | Administration and Management | Customer and Personal Service | Engineering and Technology | Public Safety and Security</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک | اداری | مدیریت و اداره | خدمات مشتری و شخصی | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Speech Clarity | Written Expression | Deductive Reasoning | Near Vision | Speech Recognition | Problem Sensitivity | Inductive Reasoning | Fluency of Ideas | Originality | Category Flexibility | Far Vision | Selective Attention | Information Ordering | Time Sharing | Perceptual Speed</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | ترتیب‌دهی اطلاعات | تقسیم توجه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E-Mail | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Freedom to Make Decisions | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Time Pressure | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Conflict Situations | Telephone Conversations | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Public Speaking</t>
+          <t>ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | موقعیت‌های تعارض | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Career/Technical Education Teachers, Postsecondary | Career/Technical Education Teachers, Secondary School | Computer Science Teachers, Postsecondary | Education Administrators, Kindergarten through Secondary | Education Teachers, Postsecondary | Educational, Guidance, and Career Counselors and Advisors | Elementary School Teachers, Except Special Education | Family and Consumer Sciences Teachers, Postsecondary | Instructional Coordinators | Middle School Teachers, Except Special and Career/Technical Education | Secondary School Teachers, Except Special and Career/Technical Education | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Middle School | Special Education Teachers, Secondary School | Teaching Assistants, Postsecondary | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education | Tutors</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | اساتید علوم رایانه، پس از متوسطه | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. | Assign and grade class work and homework. | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. | Attend staff meetings and serve on committees, as required. | Collaborate with other teachers and administrators in the development, evaluation, and revision of middle school programs. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. | Confer with parents or guardians, other teachers, counselors, and administrators to resolve students' behavioral and academic problems. | Enforce all administration policies and rules governing students. | Establish and enforce rules for behavior and procedures for maintaining order among students. | Establish clear objectives for all lessons, units, and projects, and communicate those objectives to students. | Guide and counsel students with adjustments, academic problems, or special academic interests. | Instruct and monitor students in the use and care of equipment and materials to prevent injuries and damage. | Instruct students individually and in groups, using various teaching methods, such as lectures, discussions, and demonstrations. | Maintain accurate and complete student records as required by laws, district policies, and administrative regulations. | Meet with other professionals to discuss individual students' needs and progress. | Meet with parents and guardians to discuss their children's progress and to determine priorities for their children and their resource needs. | Observe and evaluate students' performance, behavior, social development, and physical health. | Perform administrative duties, such as school library assistance, hall and cafeteria monitoring, and bus loading and unloading. | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. | Plan and supervise class projects, field trips, visits by guest speakers or other experiential activities, and guide students in learning from those activities. | Prepare and implement remedial programs for students requiring extra help. | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. | Prepare materials and classrooms for class activities. | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. | Prepare reports on students and activities as required by administration. | Prepare students for later educational experiences by encouraging them to explore learning opportunities and to persevere with challenging tasks. | Prepare, administer, and grade tests and assignments to evaluate students' progress. | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. | Select, store, order, issue, inventory, and maintain classroom equipment, materials, and supplies. | Sponsor extracurricular activities, such as clubs, student organizations, and academic contests. | Use computers, audio-visual aids, and other equipment and materials to supplement presentations.</t>
+          <t>Adapt teaching methods and instructional materials to meet students' varying needs and interests. (تطبیق روش‌های تدریس و مواد آموزشی برای برآورده کردن نیازها و علایق متغیر دانش‌آموزان.) | Assign and grade class work and homework. (تعیین و نمره‌دهی به تکالیف کلاسی و خانگی.) | Attend professional meetings, educational conferences, and teacher training workshops to maintain and improve professional competence. (شرکت در جلسات حرفه‌ای، کنفرانس‌های آموزشی و کارگاه‌های تربیت معلم برای حفظ و ارتقای صلاحیت حرفه‌ای.) | Attend staff meetings and serve on committees, as required. (شرکت در جلسات کارکنان و عضویت در کمیته‌ها، در صورت نیاز.) | همکاری با سایر معلمان و مدیران در تدوین، ارزیابی و بازنگری برنامه‌های دوره متوسطه اول. | Confer with other staff members to plan and schedule lessons promoting learning, following approved curricula. (مشورت با سایر اعضای کارکنان برای برنامه‌ریزی و زمان‌بندی درس‌هایی که یادگیری را ارتقا می‌دهند، با پیروی از برنامه‌های درسی مصوب.) | Confer with parents or guardians, other teachers, counselors, and administrators to resolve students' behavioral and academic problems. (مشورت با والدین یا سرپرستان، سایر معلمان، مشاوران و مدیران برای حل مشکلات رفتاری و تحصیلی دانش‌آموزان.) | Enforce all administration policies and rules governing students. (اجرای تمام سیاست‌ها و قوانین اداری حاکم بر دانش‌آموزان.) | Establish and enforce rules for behavior and procedures for maintaining order among students. (ایجاد و اجرای قوانین رفتاری و رویه‌های حفظ نظم در میان دانش‌آموزان.) | Establish clear objectives for all lessons, units, and projects, and communicate those objectives to students. (تعیین اهداف روشن برای تمام درس‌ها، واحدها و پروژه‌ها، و ابلاغ آن اهداف به دانش‌آموزان.) | Guide and counsel students with adjustments, academic problems, or special academic interests. (راهنمایی و مشاوره به دانش‌آموزان در خصوص سازگاری، مشکلات تحصیلی یا علایق تحصیلی خاص.) | Instruct and monitor students in the use and care of equipment and materials to prevent injuries and damage. (آموزش و نظارت بر دانش‌آموزان در استفاده و مراقبت از تجهیزات و مواد برای جلوگیری از آسیب و خسارت.) | Instruct students individually and in groups, using various teaching methods, such as lectures, discussions, and demonstrations. (آموزش دانش‌آموزان به صورت فردی و گروهی، با استفاده از روش‌های تدریس مختلف، مانند سخنرانی، بحث و نمایش.) | سوابق دقیق و کامل دانش‌آموزان را طبق قوانین، سیاست‌های منطقه و مقررات اداری نگهداری کنید. | Meet with other professionals to discuss individual students' needs and progress. (ملاقات با سایر متخصصان برای بحث در مورد نیازها و پیشرفت دانش‌آموزان به صورت فردی.) | Meet with parents and guardians to discuss their children's progress and to determine priorities for their children and their resource needs. (ملاقات با والدین و سرپرستان برای بحث در مورد پیشرفت فرزندانشان و تعیین اولویت‌ها برای فرزندان و نیازهای منابع آن‌ها.) | Observe and evaluate students' performance, behavior, social development, and physical health. (مشاهده و ارزیابی عملکرد، رفتار، رشد اجتماعی و سلامت جسمانی دانش‌آموزان.) | Perform administrative duties, such as school library assistance, hall and cafeteria monitoring, and bus loading and unloading. (انجام وظایف اداری، مانند کمک به کتابخانه مدرسه، نظارت بر سالن و کافه‌تریا، و سوار و پیاده کردن اتوبوس.) | Plan and conduct activities for a balanced program of instruction, demonstration, and work time that provides students with opportunities to observe, question, and investigate. (برنامه‌ریزی و اجرای فعالیت‌ها برای یک برنامه متعادل از آموزش، نمایش و زمان کار که فرصت‌هایی را برای مشاهده، پرسش و تحقیق برای دانش‌آموزان فراهم می‌کند.) | Plan and supervise class projects, field trips, visits by guest speakers or other experiential activities, and guide students in learning from those activities. (برنامه‌ریزی و نظارت بر پروژه‌های کلاسی، اردوهای علمی، بازدید سخنرانان مهمان یا سایر فعالیت‌های تجربی، و راهنمایی دانش‌آموزان در یادگیری از آن فعالیت‌ها.) | Prepare and implement remedial programs for students requiring extra help. (آماده‌سازی و اجرای برنامه‌های جبرانی برای دانش‌آموزانی که به کمک بیشتری نیاز دارند.) | Prepare for assigned classes and show written evidence of preparation upon request of immediate supervisors. (آماده‌سازی برای کلاس‌های محول‌شده و ارائه شواهد کتبی از آمادگی در صورت درخواست سرپرستان مستقیم.) | Prepare materials and classrooms for class activities. (آماده‌سازی مواد و کلاس‌های درس برای فعالیت‌های کلاسی.) | Prepare objectives and outlines for courses of study, following curriculum guidelines or requirements of states and schools. (آماده‌سازی اهداف و رئوس مطالب برای دوره‌های تحصیلی، با پیروی از دستورالعمل‌های برنامه درسی یا الزامات ایالت‌ها و مدارس.) | Prepare reports on students and activities as required by administration. (آماده‌سازی گزارش‌ها در مورد دانش‌آموزان و فعالیت‌ها طبق الزامات مدیریت.) | دانش‌آموزان را برای تجربیات آموزشی بعدی آماده کنید و آن‌ها را تشویق کنید تا فرصت‌های یادگیری را کشف کنند و در کارهای چالش‌برانگیز پشتکار داشته باشند. | Prepare, administer, and grade tests and assignments to evaluate students' progress. (آماده‌سازی، اجرا و نمره‌دهی به آزمون‌ها و تکالیف برای ارزیابی پیشرفت دانش‌آموزان.) | Provide students with disabilities with assistive devices, supportive technology, and assistance accessing facilities, such as restrooms. (ارائه وسایل کمکی، فناوری حمایتی و کمک به دسترسی به امکاناتی مانند سرویس‌های بهداشتی به دانش‌آموزان دارای معلولیت.) | انتخاب، نگهداری، سفارش، تحویل، انبارگردانی و مراقبت از تجهیزات، مواد و ملزومات کلاس درس. | Sponsor extracurricular activities, such as clubs, student organizations, and academic contests. (حمایت از فعالیت‌های فوق‌برنامه، مانند باشگاه‌ها، سازمان‌های دانش‌آموزی و مسابقات علمی.) | Use computers, audio-visual aids, and other equipment and materials to supplement presentations. (استفاده از کامپیوتر، وسایل کمک آموزشی دیداری-شنیداری و سایر تجهیزات و مواد برای تکمیل ارائه‌ها.)</t>
         </is>
       </c>
     </row>

--- a/data_extactor/batch_10_fa/batch_0034_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0034_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | زبان انگلیسی | آموزش و تدریس | تاریخ و باستان‌شناسی | جامعه‌شناسی و مردم‌شناسی | حقوق و امور دولتی</t>
+          <t>فلسفه و الهیات | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | دید نزدیک | حساسیت به مسئله | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | حافظه | روانی بیان ایده‌ها</t>
+          <t>درک کتبی | بیان شفاهی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | مدرسان مردم‌شناسی و باستان‌شناسی در آموزش عالی | مدرسان مطالعات منطقه‌ای، قومیتی و فرهنگی در آموزش عالی | مدرسان علوم ارتباطات در آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدرسان زبان‌ها و ادبیات خارجی در آموزش عالی | مدرسان جغرافیا در آموزش عالی | مدرسان تاریخ در آموزش عالی | مدرسان حقوق در آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان علوم سیاسی در آموزش عالی | مدرسان روان‌شناسی در آموزش عالی | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در آموزش عالی | مدرسان جامعه‌شناسی در آموزش عالی | دستیاران آموزشی در آموزش عالی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | روان‌شناسی | مدیریت و امور اداری | ریاضیات | رایانه و الکترونیک | امور دفتری و اداری | جامعه‌شناسی و مردم‌شناسی | ارتباطات و رسانه | حقوق و امور دولتی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | اداری | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | ابتکار و خلاقیت | روانی بیان ایده‌ها</t>
+          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | مدرسان علوم دامی و کشاورزی در آموزش عالی | مدرسان مدیریت و بازرگانی در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | معلمان آموزش فنی‌وحرفه‌ای دوره دوم متوسطه | مدرسان علوم تربیتی در آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان آموزش سلامت و بهداشت | مدرسان علوم و تخصص‌های پیراپزشکی در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | مدرسان علم اطلاعات و دانش‌شناسی در آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان روان‌شناسی در آموزش عالی | مدرسان علوم ورزشی و اوقات فراغت در آموزش عالی | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در آموزش عالی | مدرسان جامعه‌شناسی در آموزش عالی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره دوم متوسطه</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان آموزش بهداشت و ارتقای سلامت | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان روان‌شناسی دانشگاه | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | دبیران آموزش استثنایی دوره دوم متوسطه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک | روان‌شناسی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ریاضیات | درمان و مشاوره | ارتباطات و رسانه | پزشکی و دندان‌پزشکی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | درمان و مشاوره | ارتباطات و رسانه | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | روانی بیان ایده‌ها | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | حساسیت به مسئله | توجه انتخابی | ابتکار و خلاقیت</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارشناسان تربیت بدنی انطباقی و استثنایی | مدرسان علوم زیستی در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | مدرسان آموزش فنی‌وحرفه‌ای در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره دوم متوسطه | مدرسان علوم تربیتی در آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم محیط‌زیست در آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان برنامه‌ریزی تندرستی و سلامت | مدرسان علوم و تخصص‌های پیراپزشکی در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | مدرسان و مربیان پرستاری در آموزش عالی | مدرسان روان‌شناسی در آموزش عالی | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان دوره‌های آزاد و مهارت‌های فردی | مدرسان مددکاری اجتماعی در آموزش عالی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی</t>
+          <t>متخصصان تربیت بدنی انطباقی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مربیان و استادان پرستاری دانشگاه | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>راهبردهای یادگیری | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | مکانیک | ریاضیات | خدمات مشتریان و خدمات فردی | امور دفتری و اداری | مهندسی و فناوری | رایانه و الکترونیک | مدیریت و امور اداری | ایمنی و امنیت عمومی | طراحی | شیمی | امور پرسنلی و منابع انسانی | فیزیک</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مکانیک | ریاضیات | خدمات مشتری و شخصی | اداری | مهندسی و فناوری | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی | طراحی | شیمی | پرسنل و منابع انسانی | فیزیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | توجه انتخابی | ابتکار و خلاقیت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی خودرو | مدرسان مدیریت و بازرگانی در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | معلمان آموزش فنی‌وحرفه‌ای دوره دوم متوسطه | مدرسان علوم کامپیوتر در آموزش عالی | مدرسان مهندسی در آموزش عالی | مدرسان علوم و تخصص‌های پیراپزشکی در آموزش عالی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مدرسان علوم ورزشی و اوقات فراغت در آموزش عالی | مدرسان دوره‌های آزاد و مهارت‌های فردی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی | کارشناسان آموزش و توانمندسازی منابع انسانی | مدرسان خصوصی</t>
+          <t>تکنسین‌های مهندسی خودرو | استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | استادان علوم رایانه، آموزش عالی | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کارشناسان آموزش و توسعه منابع انسانی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | روان‌شناسی | مدیریت و امور اداری | ریاضیات | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | روان‌شناسی | مدیریت و اداره | ریاضیات | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی بیان ایده‌ها | ابتکار و خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم فضایی | حافظه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدرسان مدیریت و بازرگانی در آموزش عالی | مدرسان علوم کامپیوتر در آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | مدرسان علوم و تخصص‌های پیراپزشکی در آموزش عالی | مدرسان علوم ارتباطات در آموزش عالی | مدرسان زبان و ادبیات انگلیسی در آموزش عالی | مدرسان زبان‌ها و ادبیات خارجی در آموزش عالی | مدرسان هنر، تئاتر و موسیقی در آموزش عالی | مدرسان آموزش فنی‌وحرفه‌ای در آموزش عالی | مدرسان علوم ورزشی و اوقات فراغت در آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در آموزش عالی | سایر مدرسان علوم اجتماعی در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | مدیران امور آموزشی دانشگاه‌ها و مؤسسات آموزش عالی | مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | مدرسان دوره‌های آزاد و مهارت‌های فردی | مدرسان خصوصی | کارشناسان آموزش و توانمندسازی منابع انسانی | مشاوران و کارشناسان هدایت تحصیلی و شغلی</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | استادان علوم رایانه، آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | سایر استادان علوم اجتماعی دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران آموزش عالی | مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان خصوصی و مدرسان تقویتی | کارشناسان آموزش و توسعه منابع انسانی | مشاوران تحصیلی، شغلی و هدایت استعدادها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | روان‌شناسی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | ابتکار و خلاقیت | روانی بیان ایده‌ها | تشخیص گفتار | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | دید نزدیک | بیان کتبی | دید دور | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | اصالت | روانی ایده‌ها | تشخیص گفتار | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | بینایی دور | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | مربیان نگهداری کودک | مدیران مدارس ابتدایی و متوسطه | مدیران مهدهای کودک و مراکز پیش‌دبستانی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | روان‌شناسان مدرسه | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان دوره‌های آزاد و مهارت‌های فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی | مربیان و کمک‌آموزگاران آموزش استثنایی | مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مربیان و مراقبان کودک | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نگارش</t>
+          <t>نظارت | راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | روان‌شناسی | ریاضیات | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | ایمنی و امنیت عمومی | امور دفتری و اداری | درمان و مشاوره | رایانه و الکترونیک | جغرافیا</t>
+          <t>آموزش و پرورش | زبان انگلیسی | روان‌شناسی | ریاضیات | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | ایمنی و امنیت عمومی | اداری | درمان و مشاوره | رایانه و الکترونیک | جغرافیا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | روانی بیان ایده‌ها | تشخیص گفتار | استدلال قیاسی | ابتکار و خلاقیت | استدلال استقرایی | مرتب‌سازی اطلاعات | توجه انتخابی | دید نزدیک | انعطاف‌پذیری در دسته‌بندی | اشتراک زمانی</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | استدلال قیاسی | اصالت | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | مدرسان علوم تربیتی در آموزش عالی | مدیران مهدهای کودک و مراکز پیش‌دبستانی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان دوره‌های آزاد و مهارت‌های فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | معلمان حق‌التدریس و جانشین کوتاه‌مدت | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی | مربیان و کمک‌آموزگاران آموزش استثنایی | مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | معلمان حق‌التدریس و جانشین کوتاه‌مدت | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | ریاضیات | خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | رایانه و الکترونیک | ایمنی و امنیت عمومی | امور دفتری و اداری | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | رایانه و الکترونیک | ایمنی و امنیت عمومی | اداری | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | روانی بیان ایده‌ها | استدلال قیاسی | مرتب‌سازی اطلاعات | دید نزدیک | ابتکار و خلاقیت | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | دید دور | اشتراک زمانی | انعطاف‌پذیری در ادراک الگوها | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | اصالت | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | تقسیم توجه | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | مدرسان هنر، تئاتر و موسیقی در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | مدیران مدارس ابتدایی و متوسطه | مدرسان علوم تربیتی در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان دوره‌های آزاد و مهارت‌های فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی | مربیان و کمک‌آموزگاران آموزش استثنایی | مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | فلسفه و الهیات | ریاضیات | روان‌شناسی | رایانه و الکترونیک | تاریخ و باستان‌شناسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | امور دفتری و اداری | جغرافیا</t>
+          <t>آموزش و پرورش | زبان انگلیسی | فلسفه و الهیات | ریاضیات | روان‌شناسی | رایانه و الکترونیک | تاریخ و باستان‌شناسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | اداری | جغرافیا</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | استدلال قیاسی | دید نزدیک | تشخیص گفتار | روانی بیان ایده‌ها | استدلال استقرایی | ابتکار و خلاقیت | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | حافظه</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | استدلال استقرایی | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | مدرسان هنر، تئاتر و موسیقی در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | مدیران مدارس ابتدایی و متوسطه | مدرسان علوم تربیتی در آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان دوره‌های آزاد و مهارت‌های فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی | مربیان و کمک‌آموزگاران آموزش استثنایی | مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | روان‌شناسی | رایانه و الکترونیک | امور دفتری و اداری | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک | اداری | مدیریت و اداره | خدمات مشتری و شخصی | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | روانی بیان ایده‌ها | ابتکار و خلاقیت | انعطاف‌پذیری در دسته‌بندی | دید دور | توجه انتخابی | مرتب‌سازی اطلاعات | اشتراک زمانی | سرعت ادراک</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | ترتیب‌دهی اطلاعات | تقسیم توجه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیرفارسی‌زبانان | مدرسان آموزش فنی‌وحرفه‌ای در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره دوم متوسطه | مدرسان علوم کامپیوتر در آموزش عالی | مدیران مدارس ابتدایی و متوسطه | مدرسان علوم تربیتی در آموزش عالی | مشاوران و کارشناسان هدایت تحصیلی و شغلی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی | مربیان و کمک‌آموزگاران آموزش استثنایی | مدرسان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | استادان علوم رایانه، آموزش عالی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
